--- a/tests/fixtures/expected/export_data_bermasalah.xlsx
+++ b/tests/fixtures/expected/export_data_bermasalah.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ringkasan Masalah" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Data Bermasalah" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Peserta Perlu Dicek" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan Masalah" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Bermasalah" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peserta Perlu Dicek" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>Jenis Kelamin</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dr. Citra</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -673,7 +673,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dr. Ana</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -717,7 +717,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dr. Citra</t>
+          <t>P</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -757,7 +757,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dr. Citra</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dr. Ana</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -845,7 +845,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dr. Bima</t>
+          <t>P</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dr. Bima</t>
+          <t>P</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -983,7 +983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -994,19 +994,19 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Jenis Kelamin</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>NIM</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Prodi</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Kelas Umum</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Kode Kelas PAI</t>
@@ -1014,55 +1014,50 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>Nama dari File Nilai</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Nama dari File Nilai</t>
+          <t>Presensi</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Presensi</t>
+          <t>Bacaan</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Bacaan</t>
+          <t>Hafalan</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Hafalan</t>
+          <t>Evaluasi</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Evaluasi</t>
+          <t>Total Nilai</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Total Nilai</t>
+          <t>Abjad</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Abjad</t>
+          <t>Status Nilai</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Status Nilai</t>
+          <t>Status Validasi</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Status Validasi</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Catatan Validasi</t>
         </is>
@@ -1076,19 +1071,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>240002</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Teknik Informatika</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TI-A</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>1A</t>
@@ -1096,31 +1091,26 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dr. Ana</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
           <t>Bagas Pratama</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Belum Ada Nilai</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Belum Ada Nilai</t>
+          <t>Perlu Dicek</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
-        <is>
-          <t>Perlu Dicek</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
         <is>
           <t>Abjad kosong; Total Nilai kosong</t>
         </is>
@@ -1134,19 +1124,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>240003</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Sistem Informasi</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SI-B</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>2B</t>
@@ -1154,27 +1144,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dr. Bima</t>
+          <t>Siti Rahma</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Siti Rahma</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1184,25 +1174,20 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Sudah Ada Nilai</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Sudah Ada Nilai</t>
+          <t>Perlu Dicek</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
-        <is>
-          <t>Perlu Dicek</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
         <is>
           <t>Nama berbeda; PRESENSI di luar rentang 0-100</t>
         </is>
@@ -1216,19 +1201,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>240005</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Manajemen</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>MN-A</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>10A</t>
@@ -1236,12 +1221,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dr. Citra</t>
+          <t>Eka Wulandari</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eka Wulandari</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1259,28 +1244,23 @@
           <t>90</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Sudah Ada Nilai</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Sudah Ada Nilai</t>
+          <t>Perlu Dicek</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
-        <is>
-          <t>Perlu Dicek</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
         <is>
           <t>Total Nilai kosong</t>
         </is>
@@ -1294,47 +1274,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>240006</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Manajemen</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>MN-A</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>10A</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Dr. Citra</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Belum Ada Nilai</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Belum Ada Nilai</t>
+          <t>Perlu Dicek</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
-        <is>
-          <t>Perlu Dicek</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
         <is>
           <t>Abjad kosong; Total Nilai kosong</t>
         </is>
